--- a/02_Database/Vehicle_Data.xlsx
+++ b/02_Database/Vehicle_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ge59tor\git\repos_lehre\Customer-Oriented-Concept-Assessment-COCA-Tool\02_Database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philipp/Nextcloud2/20_code/coca/02_Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7024F92-8BB0-4A1B-B642-9A3234C638FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75DAB52-171A-CE4F-BD22-4AA3817805AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="825" yWindow="-120" windowWidth="37695" windowHeight="21840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60" yWindow="560" windowWidth="25520" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vehicle Data" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="380">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -1299,6 +1299,21 @@
   </si>
   <si>
     <t>https://www.adac.de/rund-ums-fahrzeug/autokatalog/marken-modelle/vw/golf/vii-facelift/266575/#kosten</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz</t>
+  </si>
+  <si>
+    <t>EQV 300 lang</t>
+  </si>
+  <si>
+    <t>225/55 R17</t>
+  </si>
+  <si>
+    <t>90 kWh</t>
+  </si>
+  <si>
+    <t>https://www.adac.de/rund-ums-fahrzeug/autokatalog/marken-modelle/mercedes-benz/eqv/447-facelift/336102/#karosserie-und-fahrwerk</t>
   </si>
 </sst>
 </file>
@@ -1309,7 +1324,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1447,9 +1462,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Komma" xfId="1" builtinId="3"/>
-    <cellStyle name="Link" xfId="2" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1470,9 +1485,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1510,7 +1525,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1616,7 +1631,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1758,7 +1773,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1766,17 +1781,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6B5C9A0-420C-491A-ABC7-ADFF42C42C62}">
-  <dimension ref="A1:BO66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15"/>
+  <dimension ref="A1:BP66"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="59" max="60" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="11.5703125" customWidth="1"/>
-    <col min="67" max="67" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="29.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="59" max="60" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="11.5" customWidth="1"/>
+    <col min="67" max="67" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>151</v>
       </c>
@@ -1972,8 +1987,11 @@
       <c r="BO1" t="s">
         <v>321</v>
       </c>
+      <c r="BP1" t="s">
+        <v>376</v>
+      </c>
     </row>
-    <row r="2" spans="1:67">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>152</v>
       </c>
@@ -2169,13 +2187,16 @@
       <c r="BO2" t="s">
         <v>322</v>
       </c>
+      <c r="BP2" t="s">
+        <v>375</v>
+      </c>
     </row>
-    <row r="3" spans="1:67">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:67">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>123</v>
       </c>
@@ -2371,8 +2392,11 @@
       <c r="BO5" t="s">
         <v>301</v>
       </c>
+      <c r="BP5" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="6" spans="1:67">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>126</v>
       </c>
@@ -2571,8 +2595,11 @@
       <c r="BO6">
         <v>100</v>
       </c>
+      <c r="BP6">
+        <v>150</v>
+      </c>
     </row>
-    <row r="7" spans="1:67">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>126</v>
       </c>
@@ -2771,8 +2798,11 @@
       <c r="BO7">
         <v>136</v>
       </c>
+      <c r="BP7">
+        <v>204</v>
+      </c>
     </row>
-    <row r="8" spans="1:67">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>127</v>
       </c>
@@ -2972,7 +3002,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="9" spans="1:67">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>129</v>
       </c>
@@ -3171,8 +3201,11 @@
       <c r="BO9">
         <v>245</v>
       </c>
+      <c r="BP9">
+        <v>365</v>
+      </c>
     </row>
-    <row r="10" spans="1:67">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>130</v>
       </c>
@@ -3372,7 +3405,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="11" spans="1:67">
+    <row r="11" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>103</v>
       </c>
@@ -3571,8 +3604,11 @@
       <c r="BO11">
         <v>9.5</v>
       </c>
+      <c r="BP11">
+        <v>12.1</v>
+      </c>
     </row>
-    <row r="12" spans="1:67">
+    <row r="12" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>104</v>
       </c>
@@ -3771,8 +3807,11 @@
       <c r="BO12">
         <v>140</v>
       </c>
+      <c r="BP12">
+        <v>140</v>
+      </c>
     </row>
-    <row r="13" spans="1:67">
+    <row r="13" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>122</v>
       </c>
@@ -4035,8 +4074,12 @@
         <f>(0.5*0.9-0.012)/(1+(0.26-0.04*BO43/1000)*0.9)*100</f>
         <v>37.206046747104217</v>
       </c>
+      <c r="BP13">
+        <f>(0.5*0.9-0.012)/(1+(0.26-0.04*BP43/1000)*0.9)*100</f>
+        <v>38.729118992123304</v>
+      </c>
     </row>
-    <row r="14" spans="1:67">
+    <row r="14" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
         <v>155</v>
       </c>
@@ -4235,8 +4278,11 @@
       <c r="BO14">
         <v>1</v>
       </c>
+      <c r="BP14">
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="1:67">
+    <row r="15" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>105</v>
       </c>
@@ -4435,19 +4481,22 @@
       <c r="BO15">
         <v>10.6</v>
       </c>
+      <c r="BP15">
+        <v>13.7</v>
+      </c>
     </row>
-    <row r="16" spans="1:67">
+    <row r="16" spans="1:68" x14ac:dyDescent="0.2">
       <c r="AA16" s="10"/>
       <c r="BL16" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:67">
+    <row r="17" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="18" spans="1:67">
+    <row r="18" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>134</v>
       </c>
@@ -4649,8 +4698,11 @@
       <c r="BO18">
         <v>4087</v>
       </c>
+      <c r="BP18">
+        <v>5370</v>
+      </c>
     </row>
-    <row r="19" spans="1:67">
+    <row r="19" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>135</v>
       </c>
@@ -4849,8 +4901,11 @@
       <c r="BO19">
         <v>1787</v>
       </c>
+      <c r="BP19">
+        <v>1928</v>
+      </c>
     </row>
-    <row r="20" spans="1:67">
+    <row r="20" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>136</v>
       </c>
@@ -5049,8 +5104,11 @@
       <c r="BO20">
         <v>1562</v>
       </c>
+      <c r="BP20">
+        <v>1920</v>
+      </c>
     </row>
-    <row r="21" spans="1:67">
+    <row r="21" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>120</v>
       </c>
@@ -5186,7 +5244,7 @@
         <v>0.88390928725701945</v>
       </c>
       <c r="AJ21">
-        <f t="shared" ref="AJ21:BO21" si="3">AJ20/AJ19</f>
+        <f t="shared" ref="AJ21:BP21" si="3">AJ20/AJ19</f>
         <v>0.81043956043956045</v>
       </c>
       <c r="AK21">
@@ -5313,8 +5371,12 @@
         <f t="shared" si="3"/>
         <v>0.87409065472859537</v>
       </c>
+      <c r="BP21">
+        <f t="shared" si="3"/>
+        <v>0.99585062240663902</v>
+      </c>
     </row>
-    <row r="22" spans="1:67">
+    <row r="22" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>156</v>
       </c>
@@ -5450,7 +5512,7 @@
         <v>2.7990226023213194</v>
       </c>
       <c r="AJ22">
-        <f t="shared" ref="AJ22:BO22" si="5">AJ18/AJ20</f>
+        <f t="shared" ref="AJ22:BP22" si="5">AJ18/AJ20</f>
         <v>3.0305084745762714</v>
       </c>
       <c r="AK22">
@@ -5577,8 +5639,12 @@
         <f t="shared" si="5"/>
         <v>2.6165172855313701</v>
       </c>
+      <c r="BP22">
+        <f t="shared" si="5"/>
+        <v>2.796875</v>
+      </c>
     </row>
-    <row r="23" spans="1:67">
+    <row r="23" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>119</v>
       </c>
@@ -5777,8 +5843,11 @@
       <c r="BO23">
         <v>2588</v>
       </c>
+      <c r="BP23">
+        <v>3430</v>
+      </c>
     </row>
-    <row r="24" spans="1:67">
+    <row r="24" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>117</v>
       </c>
@@ -5980,8 +6049,11 @@
       <c r="BO24" s="16">
         <v>900</v>
       </c>
+      <c r="BP24">
+        <v>895</v>
+      </c>
     </row>
-    <row r="25" spans="1:67">
+    <row r="25" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>118</v>
       </c>
@@ -6183,8 +6255,11 @@
       <c r="BO25" s="16">
         <v>900</v>
       </c>
+      <c r="BP25">
+        <v>1045</v>
+      </c>
     </row>
-    <row r="26" spans="1:67">
+    <row r="26" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>138</v>
       </c>
@@ -6383,8 +6458,11 @@
       <c r="BO26" t="s">
         <v>304</v>
       </c>
+      <c r="BP26" t="s">
+        <v>377</v>
+      </c>
     </row>
-    <row r="27" spans="1:67">
+    <row r="27" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>121</v>
       </c>
@@ -6647,13 +6725,17 @@
         <f>195*0.55*2+25.4*16</f>
         <v>620.9</v>
       </c>
+      <c r="BP27">
+        <f>225*0.55*2 + 25.4*17</f>
+        <v>679.3</v>
+      </c>
     </row>
-    <row r="29" spans="1:67">
+    <row r="29" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:67">
+    <row r="30" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>108</v>
       </c>
@@ -6852,8 +6934,11 @@
       <c r="BO30" s="16">
         <v>800</v>
       </c>
+      <c r="BP30">
+        <v>1070</v>
+      </c>
     </row>
-    <row r="31" spans="1:67">
+    <row r="31" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>110</v>
       </c>
@@ -7052,8 +7137,11 @@
       <c r="BO31" s="16">
         <v>900</v>
       </c>
+      <c r="BP31">
+        <v>1070</v>
+      </c>
     </row>
-    <row r="32" spans="1:67">
+    <row r="32" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>109</v>
       </c>
@@ -7276,8 +7364,11 @@
       <c r="BO32" s="16">
         <v>1000</v>
       </c>
+      <c r="BP32">
+        <v>1100</v>
+      </c>
     </row>
-    <row r="33" spans="1:67">
+    <row r="33" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>111</v>
       </c>
@@ -7476,18 +7567,21 @@
       <c r="BO33">
         <v>68</v>
       </c>
+      <c r="BP33">
+        <v>69</v>
+      </c>
     </row>
-    <row r="34" spans="1:67">
+    <row r="34" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:67">
+    <row r="35" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="1:67">
+    <row r="36" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>112</v>
       </c>
@@ -7686,8 +7780,11 @@
       <c r="BO36">
         <v>338</v>
       </c>
+      <c r="BP36">
+        <v>1430</v>
+      </c>
     </row>
-    <row r="37" spans="1:67">
+    <row r="37" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>115</v>
       </c>
@@ -7912,8 +8009,11 @@
       <c r="BO37" s="7">
         <v>386</v>
       </c>
+      <c r="BP37">
+        <v>362</v>
+      </c>
     </row>
-    <row r="38" spans="1:67">
+    <row r="38" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>114</v>
       </c>
@@ -8112,8 +8212,11 @@
       <c r="BO38">
         <v>5</v>
       </c>
+      <c r="BP38">
+        <v>8</v>
+      </c>
     </row>
-    <row r="39" spans="1:67">
+    <row r="39" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>113</v>
       </c>
@@ -8312,8 +8415,11 @@
       <c r="BO39">
         <v>411</v>
       </c>
+      <c r="BP39">
+        <v>637</v>
+      </c>
     </row>
-    <row r="40" spans="1:67">
+    <row r="40" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>116</v>
       </c>
@@ -8512,13 +8618,16 @@
       <c r="BO40" t="s">
         <v>323</v>
       </c>
+      <c r="BP40" t="s">
+        <v>378</v>
+      </c>
     </row>
-    <row r="42" spans="1:67">
+    <row r="42" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="43" spans="1:67">
+    <row r="43" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>102</v>
       </c>
@@ -8717,8 +8826,11 @@
       <c r="BO43">
         <v>1577</v>
       </c>
+      <c r="BP43">
+        <v>2863</v>
+      </c>
     </row>
-    <row r="44" spans="1:67" s="11" customFormat="1">
+    <row r="44" spans="1:68" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="11" t="s">
         <v>158</v>
       </c>
@@ -8934,8 +9046,11 @@
         <f>107+85</f>
         <v>192</v>
       </c>
+      <c r="BP44" s="11">
+        <v>150</v>
+      </c>
     </row>
-    <row r="45" spans="1:67" s="11" customFormat="1">
+    <row r="45" spans="1:68" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="11" t="s">
         <v>160</v>
       </c>
@@ -9135,8 +9250,11 @@
       <c r="BO45" s="11">
         <v>55</v>
       </c>
+      <c r="BP45" s="11">
+        <v>150</v>
+      </c>
     </row>
-    <row r="46" spans="1:67" s="11" customFormat="1">
+    <row r="46" spans="1:68" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>206</v>
       </c>
@@ -9273,7 +9391,7 @@
         <v>20.48</v>
       </c>
       <c r="AJ46" s="12">
-        <f t="shared" ref="AJ46:BO46" si="9">(AJ44+AJ45)*12/$B$56*100</f>
+        <f t="shared" ref="AJ46:BP46" si="9">(AJ44+AJ45)*12/$B$56*100</f>
         <v>19.36</v>
       </c>
       <c r="AK46" s="12">
@@ -9400,8 +9518,12 @@
         <f t="shared" si="9"/>
         <v>19.759999999999998</v>
       </c>
+      <c r="BP46" s="12">
+        <f t="shared" si="9"/>
+        <v>24</v>
+      </c>
     </row>
-    <row r="47" spans="1:67">
+    <row r="47" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>146</v>
       </c>
@@ -9600,8 +9722,11 @@
       <c r="BO47">
         <v>0</v>
       </c>
+      <c r="BP47">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:67">
+    <row r="48" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>106</v>
       </c>
@@ -9800,8 +9925,11 @@
       <c r="BO48">
         <v>38790</v>
       </c>
+      <c r="BP48">
+        <v>80000</v>
+      </c>
     </row>
-    <row r="49" spans="1:67">
+    <row r="49" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>1</v>
       </c>
@@ -10000,8 +10128,11 @@
       <c r="BO49">
         <v>0</v>
       </c>
+      <c r="BP49">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="1:67">
+    <row r="50" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>149</v>
       </c>
@@ -10197,8 +10328,11 @@
       <c r="BO50">
         <v>17.7</v>
       </c>
+      <c r="BP50">
+        <v>27.4</v>
+      </c>
     </row>
-    <row r="51" spans="1:67">
+    <row r="51" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>107</v>
       </c>
@@ -10337,7 +10471,7 @@
         <v>5.0149999999999997</v>
       </c>
       <c r="AJ51">
-        <f t="shared" ref="AJ51:BO51" si="11">1.6*AJ47 + 0.295*AJ50</f>
+        <f t="shared" ref="AJ51:BP51" si="11">1.6*AJ47 + 0.295*AJ50</f>
         <v>4.0709999999999997</v>
       </c>
       <c r="AK51">
@@ -10464,8 +10598,12 @@
         <f t="shared" si="11"/>
         <v>5.2214999999999998</v>
       </c>
+      <c r="BP51">
+        <f t="shared" si="11"/>
+        <v>8.0829999999999984</v>
+      </c>
     </row>
-    <row r="54" spans="1:67" s="14" customFormat="1">
+    <row r="54" spans="1:68" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="13" t="s">
         <v>157</v>
       </c>
@@ -10661,8 +10799,11 @@
       <c r="BO54" s="14" t="s">
         <v>324</v>
       </c>
+      <c r="BP54" s="14" t="s">
+        <v>379</v>
+      </c>
     </row>
-    <row r="55" spans="1:67">
+    <row r="55" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>162</v>
       </c>
@@ -10670,7 +10811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:67">
+    <row r="56" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>163</v>
       </c>
@@ -10678,7 +10819,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="58" spans="1:67">
+    <row r="58" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>166</v>
       </c>
@@ -10692,7 +10833,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="59" spans="1:67">
+    <row r="59" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
         <v>168</v>
       </c>
@@ -10709,7 +10850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:67">
+    <row r="60" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
         <v>170</v>
       </c>
@@ -10723,7 +10864,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="61" spans="1:67">
+    <row r="61" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>193</v>
       </c>
@@ -10738,7 +10879,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="62" spans="1:67">
+    <row r="62" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
         <v>170</v>
       </c>
@@ -10750,7 +10891,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="63" spans="1:67">
+    <row r="63" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>194</v>
       </c>
@@ -10765,7 +10906,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="64" spans="1:67">
+    <row r="64" spans="1:68" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
         <v>170</v>
       </c>
@@ -10777,7 +10918,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>46</v>
       </c>
@@ -10792,7 +10933,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
         <v>170</v>
       </c>
@@ -10805,7 +10946,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="D14:BO14">
+  <conditionalFormatting sqref="D14:BP14 BP15">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -10861,195 +11002,195 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAE1F74D-B95D-4FBA-BFDF-8F61C59CDEA1}">
   <dimension ref="A1:BF40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>151</v>
       </c>
       <c r="BB1" s="9"/>
       <c r="BF1" s="9"/>
     </row>
-    <row r="2" spans="1:58">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:58">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
     </row>
-    <row r="4" spans="1:58">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:58">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:58">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:58">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:58">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="9" spans="1:58">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:58">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:58">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:58">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:58">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:58">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="15" spans="1:58">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="16" spans="1:58">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>110</v>
       </c>
